--- a/Issue Tracker AA_OBF.xlsx
+++ b/Issue Tracker AA_OBF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eknriis\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{5AB884BE-B5E7-40CC-B5E5-DCFBF86DB7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B80F4FD-95B2-49B9-B1BA-A97709605293}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="13_ncr:1_{5AB884BE-B5E7-40CC-B5E5-DCFBF86DB7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57B5CAA9-55B1-458F-84A2-AF837A03063E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{94F30213-8432-4ADA-9844-C97DB16F3E88}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" xr2:uid="{94F30213-8432-4ADA-9844-C97DB16F3E88}"/>
   </bookViews>
   <sheets>
     <sheet name="MSDP Issue" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4147" uniqueCount="1724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4201" uniqueCount="1749">
   <si>
     <t>Date</t>
   </si>
@@ -5084,6 +5084,84 @@
     <t>GNOC-India was unable to monitor Airtel East- Malawi, Madagascar, and Zambia nodes as EMS Heartbeat and Test alerts were not updating.</t>
   </si>
   <si>
+    <t xml:space="preserve"> 09/01/26</t>
+  </si>
+  <si>
+    <t>09/01/26, 11:00 AM WAT</t>
+  </si>
+  <si>
+    <t>09/01/26, 01:20 PM WAT.</t>
+  </si>
+  <si>
+    <t>02 HH: 20 MM</t>
+  </si>
+  <si>
+    <t>REQ000002094857</t>
+  </si>
+  <si>
+    <t>09/01/26, 12:34 PM WAT</t>
+  </si>
+  <si>
+    <t>09/01/26, 01:25 PM WAT</t>
+  </si>
+  <si>
+    <t>00 HH: 51 MM</t>
+  </si>
+  <si>
+    <t>REQ000002094834</t>
+  </si>
+  <si>
+    <t>9/1/26, 10:31 PM WAT</t>
+  </si>
+  <si>
+    <t>9/1/26, 11:26 PM WAT.</t>
+  </si>
+  <si>
+    <t>00 HH: 55 MM</t>
+  </si>
+  <si>
+    <t>REQ000002095044</t>
+  </si>
+  <si>
+    <t>GNOC-India is unable to monitor Airtel Madagascar nodes due to MSDP/EtigerNG/RSG connectivity issue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 09/02/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9/2/26, 1:12 AM WAT</t>
+  </si>
+  <si>
+    <t>9/2/26, 10:10 AM WAT.</t>
+  </si>
+  <si>
+    <t>08 HH: 58 MM</t>
+  </si>
+  <si>
+    <t>REQ000002095017</t>
+  </si>
+  <si>
+    <t>GNOC-India is unable to monitor Airtel Gabon nodes due to EtigerNG connectivity issue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 09/08/26</t>
+  </si>
+  <si>
+    <t>08/09/26 04:25 PM WAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 08/09/26 06:35 PM WAT</t>
+  </si>
+  <si>
+    <t>02 HH: 10 MM</t>
+  </si>
+  <si>
+    <t>REQ000002097248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNOC-India is unable to monitor Airtel Niger nodes due to Surf/EtigerNG/RSG </t>
+  </si>
+  <si>
     <t>Start Time(mm/dd/yy AM/PM)</t>
   </si>
   <si>
@@ -5262,9 +5340,6 @@
   </si>
   <si>
     <t>INC000103120571/ REQ000002095017</t>
-  </si>
-  <si>
-    <t>GNOC-India is unable to monitor Airtel Gabon nodes due to EtigerNG connectivity issue.</t>
   </si>
 </sst>
 </file>
@@ -5900,7 +5975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{786AD607-CD89-401D-B2E0-3660FB0A37ED}">
-  <dimension ref="A1:K398"/>
+  <dimension ref="A1:K403"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="15.42578125" style="2" customWidth="1"/>
@@ -19828,7 +19903,180 @@
       <c r="J398" s="46" t="s">
         <v>1662</v>
       </c>
-      <c r="K398" s="14"/>
+      <c r="K398" s="14" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="399" spans="1:11" ht="15">
+      <c r="A399" s="21" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B399" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C399" s="22" t="s">
+        <v>476</v>
+      </c>
+      <c r="D399" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E399" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F399" s="22" t="s">
+        <v>1664</v>
+      </c>
+      <c r="G399" s="22" t="s">
+        <v>1665</v>
+      </c>
+      <c r="H399" s="25" t="s">
+        <v>1666</v>
+      </c>
+      <c r="I399" s="22" t="s">
+        <v>1667</v>
+      </c>
+      <c r="J399" s="14" t="s">
+        <v>1589</v>
+      </c>
+      <c r="K399" s="14" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="400" spans="1:11" ht="15">
+      <c r="A400" s="21" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B400" s="22" t="s">
+        <v>899</v>
+      </c>
+      <c r="C400" s="22" t="s">
+        <v>476</v>
+      </c>
+      <c r="D400" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E400" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F400" s="22" t="s">
+        <v>1668</v>
+      </c>
+      <c r="G400" s="22" t="s">
+        <v>1669</v>
+      </c>
+      <c r="H400" s="25" t="s">
+        <v>1670</v>
+      </c>
+      <c r="I400" s="22" t="s">
+        <v>1671</v>
+      </c>
+      <c r="J400" s="14" t="s">
+        <v>1640</v>
+      </c>
+      <c r="K400" s="14" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="401" spans="1:11" ht="15">
+      <c r="A401" s="21" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B401" s="22" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C401" s="22" t="s">
+        <v>476</v>
+      </c>
+      <c r="D401" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E401" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F401" s="22" t="s">
+        <v>1672</v>
+      </c>
+      <c r="G401" s="22" t="s">
+        <v>1673</v>
+      </c>
+      <c r="H401" s="25" t="s">
+        <v>1674</v>
+      </c>
+      <c r="I401" s="22" t="s">
+        <v>1675</v>
+      </c>
+      <c r="J401" s="14" t="s">
+        <v>1676</v>
+      </c>
+      <c r="K401" s="14" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="402" spans="1:11" ht="15">
+      <c r="A402" s="21" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B402" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C402" s="22" t="s">
+        <v>476</v>
+      </c>
+      <c r="D402" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E402" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F402" s="22" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G402" s="22" t="s">
+        <v>1679</v>
+      </c>
+      <c r="H402" s="25" t="s">
+        <v>1680</v>
+      </c>
+      <c r="I402" s="22" t="s">
+        <v>1681</v>
+      </c>
+      <c r="J402" s="14" t="s">
+        <v>1682</v>
+      </c>
+      <c r="K402" s="14"/>
+    </row>
+    <row r="403" spans="1:11" ht="15">
+      <c r="A403" s="21" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B403" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C403" s="22" t="s">
+        <v>476</v>
+      </c>
+      <c r="D403" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E403" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F403" s="22" t="s">
+        <v>1684</v>
+      </c>
+      <c r="G403" s="22" t="s">
+        <v>1685</v>
+      </c>
+      <c r="H403" s="25" t="s">
+        <v>1686</v>
+      </c>
+      <c r="I403" s="22" t="s">
+        <v>1687</v>
+      </c>
+      <c r="J403" s="14" t="s">
+        <v>1688</v>
+      </c>
+      <c r="K403" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19866,10 +20114,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>1663</v>
+        <v>1689</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>1664</v>
+        <v>1690</v>
       </c>
       <c r="G1" s="19" t="s">
         <v>7</v>
@@ -19881,7 +20129,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>1665</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -19898,22 +20146,22 @@
         <v>14</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>1666</v>
+        <v>1692</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>1667</v>
+        <v>1693</v>
       </c>
       <c r="G2" s="27" t="s">
         <v>1308</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>1668</v>
+        <v>1694</v>
       </c>
       <c r="I2" s="22" t="s">
-        <v>1669</v>
+        <v>1695</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>1670</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -19939,13 +20187,13 @@
         <v>483</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>1668</v>
+        <v>1694</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>1671</v>
+        <v>1697</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>1670</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -19962,22 +20210,22 @@
         <v>14</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>1672</v>
+        <v>1698</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>1673</v>
+        <v>1699</v>
       </c>
       <c r="G4" s="27" t="s">
         <v>164</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>1668</v>
+        <v>1694</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>1671</v>
+        <v>1697</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>1670</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -20023,16 +20271,16 @@
         <v>4</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>1663</v>
+        <v>1689</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>1664</v>
+        <v>1690</v>
       </c>
       <c r="H1" s="36" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="34" t="s">
-        <v>1674</v>
+        <v>1700</v>
       </c>
       <c r="J1" s="37" t="s">
         <v>8</v>
@@ -20043,28 +20291,28 @@
         <v>46181</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>1675</v>
+        <v>1701</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>547</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>1676</v>
+        <v>1702</v>
       </c>
       <c r="E2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>1677</v>
+        <v>1703</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>1678</v>
+        <v>1704</v>
       </c>
       <c r="H2" s="38" t="s">
         <v>1397</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>1679</v>
+        <v>1705</v>
       </c>
       <c r="J2" s="22"/>
     </row>
@@ -20107,16 +20355,16 @@
         <v>4</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>1663</v>
+        <v>1689</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>1664</v>
+        <v>1690</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>1674</v>
+        <v>1700</v>
       </c>
       <c r="J1" s="13" t="s">
         <v>8</v>
@@ -20171,16 +20419,16 @@
         <v>4</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>1663</v>
+        <v>1689</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>1664</v>
+        <v>1690</v>
       </c>
       <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="17" t="s">
-        <v>1674</v>
+        <v>1700</v>
       </c>
       <c r="J1" s="20" t="s">
         <v>8</v>
@@ -20191,7 +20439,7 @@
         <v>46176</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>1680</v>
+        <v>1706</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>1247</v>
@@ -20203,19 +20451,19 @@
         <v>14</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>1681</v>
+        <v>1707</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>1682</v>
+        <v>1708</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>1683</v>
+        <v>1709</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>1684</v>
+        <v>1710</v>
       </c>
       <c r="J2" s="26" t="s">
-        <v>1685</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -20223,7 +20471,7 @@
         <v>46179</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>1680</v>
+        <v>1706</v>
       </c>
       <c r="C3" s="22" t="s">
         <v>476</v>
@@ -20235,19 +20483,19 @@
         <v>14</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>1686</v>
+        <v>1712</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>1687</v>
+        <v>1713</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>1688</v>
+        <v>1714</v>
       </c>
       <c r="I3" s="26" t="s">
-        <v>1689</v>
+        <v>1715</v>
       </c>
       <c r="J3" s="26" t="s">
-        <v>1690</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -20255,7 +20503,7 @@
         <v>46200</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>1680</v>
+        <v>1706</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>547</v>
@@ -20267,19 +20515,19 @@
         <v>14</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>1691</v>
+        <v>1717</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>1692</v>
+        <v>1718</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>1693</v>
+        <v>1719</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>1684</v>
+        <v>1710</v>
       </c>
       <c r="J4" s="26" t="s">
-        <v>1694</v>
+        <v>1720</v>
       </c>
     </row>
   </sheetData>
@@ -20321,16 +20569,16 @@
         <v>4</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>1663</v>
+        <v>1689</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>1664</v>
+        <v>1690</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>1674</v>
+        <v>1700</v>
       </c>
       <c r="J1" s="13" t="s">
         <v>8</v>
@@ -20341,7 +20589,7 @@
         <v>46197</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>1695</v>
+        <v>1721</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>1173</v>
@@ -20353,19 +20601,19 @@
         <v>14</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>1696</v>
+        <v>1722</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>1697</v>
+        <v>1723</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>1698</v>
+        <v>1724</v>
       </c>
       <c r="I2" s="40" t="s">
-        <v>1699</v>
+        <v>1725</v>
       </c>
       <c r="J2" s="41" t="s">
-        <v>1700</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -20385,16 +20633,16 @@
         <v>14</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>1701</v>
+        <v>1727</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>1702</v>
+        <v>1728</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>1703</v>
+        <v>1729</v>
       </c>
       <c r="I3" s="40" t="s">
-        <v>1704</v>
+        <v>1730</v>
       </c>
       <c r="J3" s="41" t="s">
         <v>1631</v>
@@ -20405,7 +20653,7 @@
         <v>46205</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>1695</v>
+        <v>1721</v>
       </c>
       <c r="C4" s="22" t="s">
         <v>476</v>
@@ -20417,19 +20665,19 @@
         <v>14</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>1705</v>
+        <v>1731</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>1706</v>
+        <v>1732</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>1707</v>
+        <v>1733</v>
       </c>
       <c r="I4" s="40" t="s">
-        <v>1708</v>
+        <v>1734</v>
       </c>
       <c r="J4" s="41" t="s">
-        <v>1709</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -20437,7 +20685,7 @@
         <v>46241</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>1695</v>
+        <v>1721</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>547</v>
@@ -20449,19 +20697,19 @@
         <v>14</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>1710</v>
+        <v>1736</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>1711</v>
+        <v>1737</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>1712</v>
+        <v>1738</v>
       </c>
       <c r="I5" s="42" t="s">
-        <v>1699</v>
+        <v>1725</v>
       </c>
       <c r="J5" s="43" t="s">
-        <v>1713</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -20507,10 +20755,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>1663</v>
+        <v>1689</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>1664</v>
+        <v>1690</v>
       </c>
       <c r="H1" s="19" t="s">
         <v>7</v>
@@ -20519,7 +20767,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="17" t="s">
-        <v>1674</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -20539,19 +20787,19 @@
         <v>14</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>1714</v>
+        <v>1740</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>1715</v>
+        <v>1741</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>1716</v>
+        <v>1742</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>1717</v>
+        <v>1743</v>
       </c>
       <c r="J2" s="45" t="s">
-        <v>1718</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15">
@@ -20571,19 +20819,19 @@
         <v>14</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>1719</v>
+        <v>1745</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>1720</v>
+        <v>1746</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>1721</v>
+        <v>1747</v>
       </c>
       <c r="I3" s="44" t="s">
-        <v>1722</v>
+        <v>1748</v>
       </c>
       <c r="J3" s="45" t="s">
-        <v>1723</v>
+        <v>1682</v>
       </c>
     </row>
   </sheetData>
@@ -20592,21 +20840,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ED8B2C8E68AE01479F545D55EB21AF0B" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1c770e52177ed3071dd2afe6eddb8d31">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1902bb6f-9742-43c7-83cd-78dfc04ff927" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9b5aab5975c58ac3b83150e37659e28a" ns2:_="">
     <xsd:import namespace="1902bb6f-9742-43c7-83cd-78dfc04ff927"/>
@@ -20744,8 +20977,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5915E7F-8352-41E1-AC23-D786F467B458}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81B62ADE-CE3E-4F60-A1C6-EF22221087A3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20753,7 +21001,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81B62ADE-CE3E-4F60-A1C6-EF22221087A3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5915E7F-8352-41E1-AC23-D786F467B458}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Issue Tracker AA_OBF.xlsx
+++ b/Issue Tracker AA_OBF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eknriis\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="13_ncr:1_{5AB884BE-B5E7-40CC-B5E5-DCFBF86DB7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57B5CAA9-55B1-458F-84A2-AF837A03063E}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{5AB884BE-B5E7-40CC-B5E5-DCFBF86DB7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2967F80-6215-4F46-BF67-50B976DF6C1F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" xr2:uid="{94F30213-8432-4ADA-9844-C97DB16F3E88}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{94F30213-8432-4ADA-9844-C97DB16F3E88}"/>
   </bookViews>
   <sheets>
     <sheet name="MSDP Issue" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4201" uniqueCount="1749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4191" uniqueCount="1744">
   <si>
     <t>Date</t>
   </si>
@@ -5126,220 +5126,205 @@
     <t>GNOC-India is unable to monitor Airtel Madagascar nodes due to MSDP/EtigerNG/RSG connectivity issue.</t>
   </si>
   <si>
-    <t xml:space="preserve"> 09/02/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 9/2/26, 1:12 AM WAT</t>
-  </si>
-  <si>
-    <t>9/2/26, 10:10 AM WAT.</t>
-  </si>
-  <si>
-    <t>08 HH: 58 MM</t>
-  </si>
-  <si>
-    <t>REQ000002095017</t>
+    <t xml:space="preserve"> 09/08/26</t>
+  </si>
+  <si>
+    <t>08/09/26 04:25 PM WAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 08/09/26 06:35 PM WAT</t>
+  </si>
+  <si>
+    <t>02 HH: 10 MM</t>
+  </si>
+  <si>
+    <t>REQ000002097248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNOC-India is unable to monitor Airtel Niger nodes due to Surf/EtigerNG/RSG </t>
+  </si>
+  <si>
+    <t>Start Time(mm/dd/yy AM/PM)</t>
+  </si>
+  <si>
+    <t>End Time (mm/dd/yy AM/PM)</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>05/15/2026 03:30 PM</t>
+  </si>
+  <si>
+    <t>15/05/2026 07:00 PM</t>
+  </si>
+  <si>
+    <t>Autocaller is not working for Airtel Africa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC1632144 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESB Issue </t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>06/13/2026 05:30 AM</t>
+  </si>
+  <si>
+    <t>06/13/2026  10:00 AM</t>
+  </si>
+  <si>
+    <t>Problem specification</t>
+  </si>
+  <si>
+    <t>Airtel-West</t>
+  </si>
+  <si>
+    <t>AA</t>
+  </si>
+  <si>
+    <t>08/06/2026, 11:30 PM</t>
+  </si>
+  <si>
+    <t>08/06/2026, 12:23 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test alerts were not updating with Current time </t>
+  </si>
+  <si>
+    <t>All Airtel Opco's and OBF</t>
+  </si>
+  <si>
+    <t>06/03/2026, 06:00 PM</t>
+  </si>
+  <si>
+    <t>06/03/2026, 09:30 PM</t>
+  </si>
+  <si>
+    <t>3 hours 30 minutes</t>
+  </si>
+  <si>
+    <t>GNOC-India is unable to create TTs for Airtel Africa, Zain NG and OBF Opco due to OneFM server connectivity issue Monitoring is fine via One FM.</t>
+  </si>
+  <si>
+    <t>REQ000002063384</t>
+  </si>
+  <si>
+    <t>06/06/2026, 04:29 AM</t>
+  </si>
+  <si>
+    <t>06/06/2026, 09:20 AM</t>
+  </si>
+  <si>
+    <t>4 hours 51 minutes</t>
+  </si>
+  <si>
+    <t>GNOC-India was unable to create Semi Auto and Auto TTs on OneFM for Airtel Africa, Zain NG and OBF Opco due to Issue at BMC Helix end, Monitoring was fine via One FM.</t>
+  </si>
+  <si>
+    <t>REQ000002064341//REQ000002064340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/27/2026, 03:41 PM </t>
+  </si>
+  <si>
+    <t>06/27/2026, 06:15 PM</t>
+  </si>
+  <si>
+    <t>2 hours 34 minutes</t>
+  </si>
+  <si>
+    <t>REQ000002072626</t>
+  </si>
+  <si>
+    <t>OBF and All Africa Opco's</t>
+  </si>
+  <si>
+    <t>06/24/26, 06:05 AM</t>
+  </si>
+  <si>
+    <t>06/24/2026, 07:35 AM</t>
+  </si>
+  <si>
+    <t>1hrs 30 mins</t>
+  </si>
+  <si>
+    <t>GNOC-India was unable to monitor OBF and all Airtel Africa Opco’s via One FM as tool connectivity was down</t>
+  </si>
+  <si>
+    <t>REQ000002070545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/30/26, 01:00 PM </t>
+  </si>
+  <si>
+    <t>06/30/2026, 01:43 PM</t>
+  </si>
+  <si>
+    <t>43 minutes</t>
+  </si>
+  <si>
+    <t>GNOC-I is unable to monitor orange Burkina faso all IN nodes as we are getting Probe down alert with current time   and Heartbeat is also stopped. Rest OPCO monitoring is fine.</t>
+  </si>
+  <si>
+    <t>07/02/26, 11:22 PM</t>
+  </si>
+  <si>
+    <t>07/03/2026, 00:38 PM</t>
+  </si>
+  <si>
+    <t>60 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GNOC-India was unable to monitor OBF and all Airtel Africa Opcos via One FM as tool connectivity was down.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ000002074598 </t>
+  </si>
+  <si>
+    <t>07/09/26, 12:55 AM</t>
+  </si>
+  <si>
+    <t>07/09/2026, 01:20 AM</t>
+  </si>
+  <si>
+    <t>20 min</t>
+  </si>
+  <si>
+    <t>REQ000002076315</t>
+  </si>
+  <si>
+    <t>06/09/2026, 12:04 AM</t>
+  </si>
+  <si>
+    <t>06/09/2026, 01:30 AM</t>
+  </si>
+  <si>
+    <t>1 hour 26 minutes</t>
+  </si>
+  <si>
+    <t>CR-20260607-00000036</t>
+  </si>
+  <si>
+    <t>GNOC-India was unable to monitor for all IN nodes in Airtel Nigeria as EMS heartbeat and test alerts were not updating due to planned activity (PCI card replacement on LKETIGER3).</t>
+  </si>
+  <si>
+    <t>9/2/26, 1:12 AM WAT</t>
+  </si>
+  <si>
+    <t>9/2/26, 10:10 AM WAT</t>
+  </si>
+  <si>
+    <t>8 hours 58 minutes</t>
+  </si>
+  <si>
+    <t>INC000103120571/ REQ000002095017</t>
   </si>
   <si>
     <t>GNOC-India is unable to monitor Airtel Gabon nodes due to EtigerNG connectivity issue.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 09/08/26</t>
-  </si>
-  <si>
-    <t>08/09/26 04:25 PM WAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 08/09/26 06:35 PM WAT</t>
-  </si>
-  <si>
-    <t>02 HH: 10 MM</t>
-  </si>
-  <si>
-    <t>REQ000002097248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNOC-India is unable to monitor Airtel Niger nodes due to Surf/EtigerNG/RSG </t>
-  </si>
-  <si>
-    <t>Start Time(mm/dd/yy AM/PM)</t>
-  </si>
-  <si>
-    <t>End Time (mm/dd/yy AM/PM)</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>05/15/2026 03:30 PM</t>
-  </si>
-  <si>
-    <t>15/05/2026 07:00 PM</t>
-  </si>
-  <si>
-    <t>Autocaller is not working for Airtel Africa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC1632144 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESB Issue </t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>06/13/2026 05:30 AM</t>
-  </si>
-  <si>
-    <t>06/13/2026  10:00 AM</t>
-  </si>
-  <si>
-    <t>Problem specification</t>
-  </si>
-  <si>
-    <t>Airtel-West</t>
-  </si>
-  <si>
-    <t>AA</t>
-  </si>
-  <si>
-    <t>08/06/2026, 11:30 PM</t>
-  </si>
-  <si>
-    <t>08/06/2026, 12:23 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test alerts were not updating with Current time </t>
-  </si>
-  <si>
-    <t>All Airtel Opco's and OBF</t>
-  </si>
-  <si>
-    <t>06/03/2026, 06:00 PM</t>
-  </si>
-  <si>
-    <t>06/03/2026, 09:30 PM</t>
-  </si>
-  <si>
-    <t>3 hours 30 minutes</t>
-  </si>
-  <si>
-    <t>GNOC-India is unable to create TTs for Airtel Africa, Zain NG and OBF Opco due to OneFM server connectivity issue Monitoring is fine via One FM.</t>
-  </si>
-  <si>
-    <t>REQ000002063384</t>
-  </si>
-  <si>
-    <t>06/06/2026, 04:29 AM</t>
-  </si>
-  <si>
-    <t>06/06/2026, 09:20 AM</t>
-  </si>
-  <si>
-    <t>4 hours 51 minutes</t>
-  </si>
-  <si>
-    <t>GNOC-India was unable to create Semi Auto and Auto TTs on OneFM for Airtel Africa, Zain NG and OBF Opco due to Issue at BMC Helix end, Monitoring was fine via One FM.</t>
-  </si>
-  <si>
-    <t>REQ000002064341//REQ000002064340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/27/2026, 03:41 PM </t>
-  </si>
-  <si>
-    <t>06/27/2026, 06:15 PM</t>
-  </si>
-  <si>
-    <t>2 hours 34 minutes</t>
-  </si>
-  <si>
-    <t>REQ000002072626</t>
-  </si>
-  <si>
-    <t>OBF and All Africa Opco's</t>
-  </si>
-  <si>
-    <t>06/24/26, 06:05 AM</t>
-  </si>
-  <si>
-    <t>06/24/2026, 07:35 AM</t>
-  </si>
-  <si>
-    <t>1hrs 30 mins</t>
-  </si>
-  <si>
-    <t>GNOC-India was unable to monitor OBF and all Airtel Africa Opco’s via One FM as tool connectivity was down</t>
-  </si>
-  <si>
-    <t>REQ000002070545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/30/26, 01:00 PM </t>
-  </si>
-  <si>
-    <t>06/30/2026, 01:43 PM</t>
-  </si>
-  <si>
-    <t>43 minutes</t>
-  </si>
-  <si>
-    <t>GNOC-I is unable to monitor orange Burkina faso all IN nodes as we are getting Probe down alert with current time   and Heartbeat is also stopped. Rest OPCO monitoring is fine.</t>
-  </si>
-  <si>
-    <t>07/02/26, 11:22 PM</t>
-  </si>
-  <si>
-    <t>07/03/2026, 00:38 PM</t>
-  </si>
-  <si>
-    <t>60 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> GNOC-India was unable to monitor OBF and all Airtel Africa Opcos via One FM as tool connectivity was down.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ000002074598 </t>
-  </si>
-  <si>
-    <t>07/09/26, 12:55 AM</t>
-  </si>
-  <si>
-    <t>07/09/2026, 01:20 AM</t>
-  </si>
-  <si>
-    <t>20 min</t>
-  </si>
-  <si>
-    <t>REQ000002076315</t>
-  </si>
-  <si>
-    <t>06/09/2026, 12:04 AM</t>
-  </si>
-  <si>
-    <t>06/09/2026, 01:30 AM</t>
-  </si>
-  <si>
-    <t>1 hour 26 minutes</t>
-  </si>
-  <si>
-    <t>CR-20260607-00000036</t>
-  </si>
-  <si>
-    <t>GNOC-India was unable to monitor for all IN nodes in Airtel Nigeria as EMS heartbeat and test alerts were not updating due to planned activity (PCI card replacement on LKETIGER3).</t>
-  </si>
-  <si>
-    <t>9/2/26, 1:12 AM WAT</t>
-  </si>
-  <si>
-    <t>9/2/26, 10:10 AM WAT</t>
-  </si>
-  <si>
-    <t>8 hours 58 minutes</t>
-  </si>
-  <si>
-    <t>INC000103120571/ REQ000002095017</t>
   </si>
 </sst>
 </file>
@@ -20017,7 +20002,7 @@
         <v>1677</v>
       </c>
       <c r="B402" s="22" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="C402" s="22" t="s">
         <v>476</v>
@@ -20045,39 +20030,7 @@
       </c>
       <c r="K402" s="14"/>
     </row>
-    <row r="403" spans="1:11" ht="15">
-      <c r="A403" s="21" t="s">
-        <v>1683</v>
-      </c>
-      <c r="B403" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C403" s="22" t="s">
-        <v>476</v>
-      </c>
-      <c r="D403" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="E403" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F403" s="22" t="s">
-        <v>1684</v>
-      </c>
-      <c r="G403" s="22" t="s">
-        <v>1685</v>
-      </c>
-      <c r="H403" s="25" t="s">
-        <v>1686</v>
-      </c>
-      <c r="I403" s="22" t="s">
-        <v>1687</v>
-      </c>
-      <c r="J403" s="14" t="s">
-        <v>1688</v>
-      </c>
-      <c r="K403" s="14"/>
-    </row>
+    <row r="403" spans="1:11" ht="15"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20114,10 +20067,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>1689</v>
+        <v>1683</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>1690</v>
+        <v>1684</v>
       </c>
       <c r="G1" s="19" t="s">
         <v>7</v>
@@ -20129,7 +20082,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>1691</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -20146,22 +20099,22 @@
         <v>14</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>1692</v>
+        <v>1686</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>1693</v>
+        <v>1687</v>
       </c>
       <c r="G2" s="27" t="s">
         <v>1308</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>1694</v>
+        <v>1688</v>
       </c>
       <c r="I2" s="22" t="s">
-        <v>1695</v>
+        <v>1689</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>1696</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -20187,13 +20140,13 @@
         <v>483</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>1694</v>
+        <v>1688</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>1697</v>
+        <v>1691</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>1696</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -20210,22 +20163,22 @@
         <v>14</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>1698</v>
+        <v>1692</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>1699</v>
+        <v>1693</v>
       </c>
       <c r="G4" s="27" t="s">
         <v>164</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>1694</v>
+        <v>1688</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>1697</v>
+        <v>1691</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>1696</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -20271,16 +20224,16 @@
         <v>4</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>1689</v>
+        <v>1683</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>1690</v>
+        <v>1684</v>
       </c>
       <c r="H1" s="36" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="34" t="s">
-        <v>1700</v>
+        <v>1694</v>
       </c>
       <c r="J1" s="37" t="s">
         <v>8</v>
@@ -20291,28 +20244,28 @@
         <v>46181</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>1701</v>
+        <v>1695</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>547</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>1702</v>
+        <v>1696</v>
       </c>
       <c r="E2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>1703</v>
+        <v>1697</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>1704</v>
+        <v>1698</v>
       </c>
       <c r="H2" s="38" t="s">
         <v>1397</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>1705</v>
+        <v>1699</v>
       </c>
       <c r="J2" s="22"/>
     </row>
@@ -20355,16 +20308,16 @@
         <v>4</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>1689</v>
+        <v>1683</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>1690</v>
+        <v>1684</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>1700</v>
+        <v>1694</v>
       </c>
       <c r="J1" s="13" t="s">
         <v>8</v>
@@ -20419,16 +20372,16 @@
         <v>4</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>1689</v>
+        <v>1683</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>1690</v>
+        <v>1684</v>
       </c>
       <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="17" t="s">
-        <v>1700</v>
+        <v>1694</v>
       </c>
       <c r="J1" s="20" t="s">
         <v>8</v>
@@ -20439,7 +20392,7 @@
         <v>46176</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>1706</v>
+        <v>1700</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>1247</v>
@@ -20451,19 +20404,19 @@
         <v>14</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>1707</v>
+        <v>1701</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>1708</v>
+        <v>1702</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>1709</v>
+        <v>1703</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>1710</v>
+        <v>1704</v>
       </c>
       <c r="J2" s="26" t="s">
-        <v>1711</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -20471,7 +20424,7 @@
         <v>46179</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>1706</v>
+        <v>1700</v>
       </c>
       <c r="C3" s="22" t="s">
         <v>476</v>
@@ -20483,19 +20436,19 @@
         <v>14</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>1712</v>
+        <v>1706</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>1713</v>
+        <v>1707</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>1714</v>
+        <v>1708</v>
       </c>
       <c r="I3" s="26" t="s">
-        <v>1715</v>
+        <v>1709</v>
       </c>
       <c r="J3" s="26" t="s">
-        <v>1716</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -20503,7 +20456,7 @@
         <v>46200</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>1706</v>
+        <v>1700</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>547</v>
@@ -20515,19 +20468,19 @@
         <v>14</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>1717</v>
+        <v>1711</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>1718</v>
+        <v>1712</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>1719</v>
+        <v>1713</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>1710</v>
+        <v>1704</v>
       </c>
       <c r="J4" s="26" t="s">
-        <v>1720</v>
+        <v>1714</v>
       </c>
     </row>
   </sheetData>
@@ -20569,16 +20522,16 @@
         <v>4</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>1689</v>
+        <v>1683</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>1690</v>
+        <v>1684</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>1700</v>
+        <v>1694</v>
       </c>
       <c r="J1" s="13" t="s">
         <v>8</v>
@@ -20589,7 +20542,7 @@
         <v>46197</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>1721</v>
+        <v>1715</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>1173</v>
@@ -20601,19 +20554,19 @@
         <v>14</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>1722</v>
+        <v>1716</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>1723</v>
+        <v>1717</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>1724</v>
+        <v>1718</v>
       </c>
       <c r="I2" s="40" t="s">
-        <v>1725</v>
+        <v>1719</v>
       </c>
       <c r="J2" s="41" t="s">
-        <v>1726</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -20633,16 +20586,16 @@
         <v>14</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>1727</v>
+        <v>1721</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>1728</v>
+        <v>1722</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>1729</v>
+        <v>1723</v>
       </c>
       <c r="I3" s="40" t="s">
-        <v>1730</v>
+        <v>1724</v>
       </c>
       <c r="J3" s="41" t="s">
         <v>1631</v>
@@ -20653,7 +20606,7 @@
         <v>46205</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>1721</v>
+        <v>1715</v>
       </c>
       <c r="C4" s="22" t="s">
         <v>476</v>
@@ -20665,19 +20618,19 @@
         <v>14</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>1731</v>
+        <v>1725</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>1732</v>
+        <v>1726</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>1733</v>
+        <v>1727</v>
       </c>
       <c r="I4" s="40" t="s">
-        <v>1734</v>
+        <v>1728</v>
       </c>
       <c r="J4" s="41" t="s">
-        <v>1735</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -20685,7 +20638,7 @@
         <v>46241</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>1721</v>
+        <v>1715</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>547</v>
@@ -20697,19 +20650,19 @@
         <v>14</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>1736</v>
+        <v>1730</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>1737</v>
+        <v>1731</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>1738</v>
+        <v>1732</v>
       </c>
       <c r="I5" s="42" t="s">
-        <v>1725</v>
+        <v>1719</v>
       </c>
       <c r="J5" s="43" t="s">
-        <v>1739</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -20755,10 +20708,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>1689</v>
+        <v>1683</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>1690</v>
+        <v>1684</v>
       </c>
       <c r="H1" s="19" t="s">
         <v>7</v>
@@ -20767,7 +20720,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="17" t="s">
-        <v>1700</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -20787,19 +20740,19 @@
         <v>14</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>1740</v>
+        <v>1734</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>1741</v>
+        <v>1735</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>1742</v>
+        <v>1736</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>1743</v>
+        <v>1737</v>
       </c>
       <c r="J2" s="45" t="s">
-        <v>1744</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15">
@@ -20819,19 +20772,19 @@
         <v>14</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>1745</v>
+        <v>1739</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>1746</v>
+        <v>1740</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>1747</v>
+        <v>1741</v>
       </c>
       <c r="I3" s="44" t="s">
-        <v>1748</v>
+        <v>1742</v>
       </c>
       <c r="J3" s="45" t="s">
-        <v>1682</v>
+        <v>1743</v>
       </c>
     </row>
   </sheetData>
@@ -20978,6 +20931,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -20986,22 +20945,16 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81B62ADE-CE3E-4F60-A1C6-EF22221087A3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49273989-39D9-4CED-AEC6-610F5F9774BB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5915E7F-8352-41E1-AC23-D786F467B458}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5915E7F-8352-41E1-AC23-D786F467B458}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49273989-39D9-4CED-AEC6-610F5F9774BB}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
